--- a/data/data_raw/eurostat/AT_bovine_population_apro_mt_lscatl.xlsx
+++ b/data/data_raw/eurostat/AT_bovine_population_apro_mt_lscatl.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO24"/>
+  <dimension ref="A1:AP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +627,11 @@
       <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -758,6 +763,7 @@
       <c r="AO2" t="n">
         <v>1820.03</v>
       </c>
+      <c r="AP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -887,6 +893,7 @@
       <c r="AO3" t="n">
         <v>579.17</v>
       </c>
+      <c r="AP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1016,6 +1023,7 @@
       <c r="AO4" t="n">
         <v>39.04</v>
       </c>
+      <c r="AP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1145,6 +1153,7 @@
       <c r="AO5" t="n">
         <v>540.13</v>
       </c>
+      <c r="AP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -1274,6 +1283,7 @@
       <c r="AO6" t="n">
         <v>415.1</v>
       </c>
+      <c r="AP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1403,6 +1413,7 @@
       <c r="AO7" t="n">
         <v>825.76</v>
       </c>
+      <c r="AP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1532,6 +1543,7 @@
       <c r="AO8" t="n">
         <v>251.46</v>
       </c>
+      <c r="AP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1665,6 +1677,7 @@
       <c r="AO9" t="n">
         <v>156.73</v>
       </c>
+      <c r="AP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1798,6 +1811,7 @@
       <c r="AO10" t="n">
         <v>24.49</v>
       </c>
+      <c r="AP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1927,6 +1941,7 @@
       <c r="AO11" t="n">
         <v>801.27</v>
       </c>
+      <c r="AP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -2056,6 +2071,7 @@
       <c r="AO12" t="n">
         <v>288.67</v>
       </c>
+      <c r="AP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -2185,6 +2201,7 @@
       <c r="AO13" t="n">
         <v>258.37</v>
       </c>
+      <c r="AP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -2314,6 +2331,7 @@
       <c r="AO14" t="n">
         <v>62.6</v>
       </c>
+      <c r="AP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -2443,6 +2461,7 @@
       <c r="AO15" t="n">
         <v>195.77</v>
       </c>
+      <c r="AP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -2572,6 +2591,7 @@
       <c r="AO16" t="n">
         <v>110.81</v>
       </c>
+      <c r="AP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -2701,6 +2721,7 @@
       <c r="AO17" t="n">
         <v>16.62</v>
       </c>
+      <c r="AP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -2830,6 +2851,7 @@
       <c r="AO18" t="n">
         <v>94.19</v>
       </c>
+      <c r="AP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -2963,6 +2985,7 @@
       <c r="AO19" t="n">
         <v>690.47</v>
       </c>
+      <c r="AP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -3096,6 +3119,7 @@
       <c r="AO20" t="n">
         <v>535.8099999999999</v>
       </c>
+      <c r="AP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -3229,6 +3253,7 @@
       <c r="AO21" t="n">
         <v>154.66</v>
       </c>
+      <c r="AP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -3358,6 +3383,7 @@
       <c r="AO22" t="n">
         <v>0</v>
       </c>
+      <c r="AP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -3487,6 +3513,7 @@
       <c r="AO23" t="n">
         <v>0</v>
       </c>
+      <c r="AP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -3616,6 +3643,7 @@
       <c r="AO24" t="n">
         <v>0</v>
       </c>
+      <c r="AP24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
